--- a/15.VLookup , HLookup & XLookup.xlsx
+++ b/15.VLookup , HLookup & XLookup.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\C\Data Science\Data Science\2.Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAE6FC6-DCA2-4627-86B9-7DAAEDE570EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0243C4B-4ABD-4379-8479-4B4F2DCAB5D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VLookup Ex 1" sheetId="1" r:id="rId1"/>
     <sheet name="VLookup Ex 2" sheetId="2" r:id="rId2"/>
     <sheet name="HLookup" sheetId="3" r:id="rId3"/>
+    <sheet name="XLookup" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="190">
   <si>
     <t>EmpNo</t>
   </si>
@@ -216,6 +217,393 @@
   </si>
   <si>
     <t>2. Show the total income for the sales of each item during the six-day period.</t>
+  </si>
+  <si>
+    <t>555-0118</t>
+  </si>
+  <si>
+    <t>isabella.reed@acme.com</t>
+  </si>
+  <si>
+    <t>San Diego</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Product Manager</t>
+  </si>
+  <si>
+    <t>Isabella</t>
+  </si>
+  <si>
+    <t>AC0018</t>
+  </si>
+  <si>
+    <t>555-0117</t>
+  </si>
+  <si>
+    <t>lucas.quinn@acme.com</t>
+  </si>
+  <si>
+    <t>Philadelphia</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>Research Associate</t>
+  </si>
+  <si>
+    <t>Lucas</t>
+  </si>
+  <si>
+    <t>AC0017</t>
+  </si>
+  <si>
+    <t>555-0116</t>
+  </si>
+  <si>
+    <t>richard.function@acme.com</t>
+  </si>
+  <si>
+    <t>Research Analyst</t>
+  </si>
+  <si>
+    <t>Richard</t>
+  </si>
+  <si>
+    <t>AC0016</t>
+  </si>
+  <si>
+    <t>555-0115</t>
+  </si>
+  <si>
+    <t>ava.parker@acme.com</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>Legal</t>
+  </si>
+  <si>
+    <t>Legal Counsel</t>
+  </si>
+  <si>
+    <t>Ava</t>
+  </si>
+  <si>
+    <t>AC0015</t>
+  </si>
+  <si>
+    <t>555-0114</t>
+  </si>
+  <si>
+    <t>henry.owens@acme.com</t>
+  </si>
+  <si>
+    <t>Nashville</t>
+  </si>
+  <si>
+    <t>Operations</t>
+  </si>
+  <si>
+    <t>Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Henry</t>
+  </si>
+  <si>
+    <t>AC0014</t>
+  </si>
+  <si>
+    <t>555-0113</t>
+  </si>
+  <si>
+    <t>ella.nelson@acme.com</t>
+  </si>
+  <si>
+    <t>Portland</t>
+  </si>
+  <si>
+    <t>Customer Success</t>
+  </si>
+  <si>
+    <t>Customer Success Manager</t>
+  </si>
+  <si>
+    <t>Ella</t>
+  </si>
+  <si>
+    <t>AC0013</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>555-0112</t>
+  </si>
+  <si>
+    <t>william.martin@acme.com</t>
+  </si>
+  <si>
+    <t>Miami</t>
+  </si>
+  <si>
+    <t>Human Resources</t>
+  </si>
+  <si>
+    <t>Recruiter</t>
+  </si>
+  <si>
+    <t>William</t>
+  </si>
+  <si>
+    <t>AC0012</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>555-0111</t>
+  </si>
+  <si>
+    <t>grace.lee@acme.com</t>
+  </si>
+  <si>
+    <t>Los Angeles</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Content Strategist</t>
+  </si>
+  <si>
+    <t>Grace</t>
+  </si>
+  <si>
+    <t>AC0011</t>
+  </si>
+  <si>
+    <t>Job Title</t>
+  </si>
+  <si>
+    <t>555-0110</t>
+  </si>
+  <si>
+    <t>robert.king@acme.com</t>
+  </si>
+  <si>
+    <t>Phoenix</t>
+  </si>
+  <si>
+    <t>Business Analyst</t>
+  </si>
+  <si>
+    <t>Robert</t>
+  </si>
+  <si>
+    <t>AC0010</t>
+  </si>
+  <si>
+    <t>555-0109</t>
+  </si>
+  <si>
+    <t>mia.johnson@acme.com</t>
+  </si>
+  <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Data Analyst</t>
+  </si>
+  <si>
+    <t>Mia</t>
+  </si>
+  <si>
+    <t>AC0009</t>
+  </si>
+  <si>
+    <t>Emp ID</t>
+  </si>
+  <si>
+    <t>555-0108</t>
+  </si>
+  <si>
+    <t>daniel.irwin@acme.com</t>
+  </si>
+  <si>
+    <t>Dallas</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Accountant</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>AC0008</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Look up by Emp ID</t>
+  </si>
+  <si>
+    <t>555-0107</t>
+  </si>
+  <si>
+    <t>sophia.harris@acme.com</t>
+  </si>
+  <si>
+    <t>San Francisco</t>
+  </si>
+  <si>
+    <t>UX Designer</t>
+  </si>
+  <si>
+    <t>Sophia</t>
+  </si>
+  <si>
+    <t>AC0007</t>
+  </si>
+  <si>
+    <t>555-0106</t>
+  </si>
+  <si>
+    <t>michael.garcia@acme.com</t>
+  </si>
+  <si>
+    <t>Denver</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Sales Executive</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>AC0006</t>
+  </si>
+  <si>
+    <t>555-0105</t>
+  </si>
+  <si>
+    <t>olivia.foster@acme.com</t>
+  </si>
+  <si>
+    <t>Austin</t>
+  </si>
+  <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>Olivia</t>
+  </si>
+  <si>
+    <t>AC0005</t>
+  </si>
+  <si>
+    <t>555-0104</t>
+  </si>
+  <si>
+    <t>james.evans@acme.com</t>
+  </si>
+  <si>
+    <t>Seattle</t>
+  </si>
+  <si>
+    <t>HR Specialist</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>AC0004</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>555-0103</t>
+  </si>
+  <si>
+    <t>emily.davis@acme.com</t>
+  </si>
+  <si>
+    <t>Boston</t>
+  </si>
+  <si>
+    <t>Marketing Manager</t>
+  </si>
+  <si>
+    <t>Emily</t>
+  </si>
+  <si>
+    <t>AC0003</t>
+  </si>
+  <si>
+    <t>555-0102</t>
+  </si>
+  <si>
+    <t>david.carter@acme.com</t>
+  </si>
+  <si>
+    <t>Chicago</t>
+  </si>
+  <si>
+    <t>Software Engineer</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>AC0002</t>
+  </si>
+  <si>
+    <t>555-0101</t>
+  </si>
+  <si>
+    <t>anna.bell@acme.com</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>Financial Analyst</t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t>AC0001</t>
+  </si>
+  <si>
+    <t>Phone No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Department </t>
+  </si>
+  <si>
+    <t>EmpID</t>
+  </si>
+  <si>
+    <t>Look up by Name</t>
   </si>
 </sst>
 </file>
@@ -225,7 +613,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,8 +660,30 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -316,8 +726,40 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B9BD5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -355,11 +797,56 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4C7E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB4C7E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB4C7E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB4C7E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -402,6 +889,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -819,7 +1318,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
@@ -833,8 +1332,8 @@
     <col min="13" max="13" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:4" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="16.8" customHeight="1"/>
+    <row r="4" spans="1:4" ht="16.2" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -848,7 +1347,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -862,7 +1361,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -876,7 +1375,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -890,7 +1389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
@@ -904,7 +1403,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -918,7 +1417,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
         <v>26</v>
       </c>
@@ -932,7 +1431,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
         <v>25</v>
       </c>
@@ -946,7 +1445,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
@@ -960,15 +1459,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+    <row r="15" spans="1:4" ht="14.4" customHeight="1">
+      <c r="A15" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-    </row>
-    <row r="17" spans="1:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+    </row>
+    <row r="17" spans="1:11" ht="17.399999999999999" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -982,7 +1481,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11">
       <c r="A18" s="2" t="s">
         <v>8</v>
       </c>
@@ -999,7 +1498,7 @@
         <v>5561243</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11">
       <c r="A19" s="2" t="s">
         <v>13</v>
       </c>
@@ -1015,12 +1514,12 @@
         <f t="shared" si="2"/>
         <v>4954959</v>
       </c>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="2" t="s">
         <v>14</v>
       </c>
@@ -1037,7 +1536,7 @@
         <v>2234567</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11">
       <c r="A21" s="2" t="s">
         <v>18</v>
       </c>
@@ -1054,7 +1553,7 @@
         <v>3365124</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11">
       <c r="A22" s="2" t="s">
         <v>25</v>
       </c>
@@ -1071,7 +1570,7 @@
         <v>4559300</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11">
       <c r="A23" s="2" t="s">
         <v>26</v>
       </c>
@@ -1088,7 +1587,7 @@
         <v>5692039</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11">
       <c r="A24" s="2" t="s">
         <v>4</v>
       </c>
@@ -1105,7 +1604,7 @@
         <v>5446578</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11">
       <c r="A25" s="2" t="s">
         <v>9</v>
       </c>
@@ -1135,22 +1634,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2539184-6B08-41D1-BDE4-1A2C0AFEBD24}">
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.109375" customWidth="1"/>
     <col min="8" max="8" width="12.44140625" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>33</v>
       </c>
@@ -1158,7 +1657,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
         <v>44</v>
       </c>
@@ -1166,7 +1665,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>46</v>
       </c>
@@ -1174,7 +1673,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
         <v>48</v>
       </c>
@@ -1182,7 +1681,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
         <v>45</v>
       </c>
@@ -1190,7 +1689,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
         <v>50</v>
       </c>
@@ -1198,7 +1697,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
         <v>51</v>
       </c>
@@ -1206,7 +1705,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
         <v>49</v>
       </c>
@@ -1214,7 +1713,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
         <v>47</v>
       </c>
@@ -1222,7 +1721,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
         <v>53</v>
       </c>
@@ -1230,7 +1729,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" s="3" t="s">
         <v>52</v>
       </c>
@@ -1238,17 +1737,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
         <v>33</v>
       </c>
@@ -1280,7 +1779,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10">
       <c r="A19" s="3" t="s">
         <v>45</v>
       </c>
@@ -1315,7 +1814,7 @@
         <v>251.54999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10">
       <c r="A20" s="3" t="s">
         <v>47</v>
       </c>
@@ -1350,7 +1849,7 @@
         <v>283.2</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10">
       <c r="A21" s="3" t="s">
         <v>49</v>
       </c>
@@ -1385,7 +1884,7 @@
         <v>138.60000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10">
       <c r="A22" s="3" t="s">
         <v>44</v>
       </c>
@@ -1420,7 +1919,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10">
       <c r="A23" s="3" t="s">
         <v>50</v>
       </c>
@@ -1455,7 +1954,7 @@
         <v>103.95</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10">
       <c r="A24" s="3" t="s">
         <v>52</v>
       </c>
@@ -1490,7 +1989,7 @@
         <v>65.25</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10">
       <c r="A25" s="3" t="s">
         <v>53</v>
       </c>
@@ -1525,7 +2024,7 @@
         <v>153.9</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10">
       <c r="A26" s="3" t="s">
         <v>46</v>
       </c>
@@ -1560,7 +2059,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10">
       <c r="A27" s="3" t="s">
         <v>48</v>
       </c>
@@ -1595,7 +2094,7 @@
         <v>178.1</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10">
       <c r="A28" s="3" t="s">
         <v>51</v>
       </c>
@@ -1641,13 +2140,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D190D11-1F25-435C-BE91-BA9AF371EC20}">
   <dimension ref="A3:I12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="5" max="5" width="11.77734375" customWidth="1"/>
     <col min="9" max="9" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" s="12" t="s">
         <v>0</v>
       </c>
@@ -1676,7 +2175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="A4" s="14" t="s">
         <v>1</v>
       </c>
@@ -1705,7 +2204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9">
       <c r="A5" s="14" t="s">
         <v>2</v>
       </c>
@@ -1734,7 +2233,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="A6" s="14" t="s">
         <v>3</v>
       </c>
@@ -1763,7 +2262,7 @@
         <v>4954959</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="A9" s="9" t="s">
         <v>0</v>
       </c>
@@ -1780,7 +2279,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="A10" s="10" t="s">
         <v>1</v>
       </c>
@@ -1801,7 +2300,7 @@
         <v>Kiran</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="A11" s="10" t="s">
         <v>2</v>
       </c>
@@ -1822,7 +2321,7 @@
         <v>Indiranagar</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9">
       <c r="A12" s="10" t="s">
         <v>3</v>
       </c>
@@ -1841,6 +2340,549 @@
       <c r="E12" s="11">
         <f>HLOOKUP(E9,$A$3:$I$6,4,0)</f>
         <v>4954959</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DDEDA98-7576-4DF8-A8DC-EB8889E37BD8}">
+  <dimension ref="A3:K23"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:11">
+      <c r="J3" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="J4" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="K5" s="18" t="str">
+        <f>_xlfn.XLOOKUP(K4,B6:B23,G6:G23,"NOT Found")</f>
+        <v>555-0112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="J6" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="K6" s="18" t="str">
+        <f>_xlfn.XLOOKUP(K4,B6:B23,C6:C23,"NOT Found")</f>
+        <v>Recruiter</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="K7" s="18" t="str">
+        <f>_xlfn.XLOOKUP(K4,B6:B23,D6:D23,"NOT Found")</f>
+        <v>Human Resources</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="K8" s="18" t="str">
+        <f>_xlfn.XLOOKUP(K4,B6:B23,E6:E23,"NOT Found")</f>
+        <v>Miami</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="J12" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="K12" s="21" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="J13" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="18" t="str">
+        <f>_xlfn.XLOOKUP(K13,A6:A23,B6:B23,"NOT Found")</f>
+        <v>Richard</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="K15" s="18" t="str">
+        <f>_xlfn.XLOOKUP(K13,A6:A23,C6:C23,"NOT Found")</f>
+        <v>Research Analyst</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="K16" s="18" t="str">
+        <f>_xlfn.XLOOKUP(K13,A6:A23,D6:D23,"NOT Found")</f>
+        <v>Research</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="J17" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="K17" s="18" t="str">
+        <f>_xlfn.XLOOKUP(K13,A6:A23,F6:F23,"NOT Found")</f>
+        <v>richard.function@acme.com</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
